--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="229">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -706,9 +706,6 @@
   </si>
   <si>
     <t>دنگ سس</t>
-  </si>
-  <si>
-    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1275,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4221,12 +4218,12 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>359000</v>
-      </c>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8">
+        <v>551000</v>
+      </c>
+      <c r="B215" s="8">
         <v>96000</v>
       </c>
+      <c r="C215" s="8"/>
       <c r="D215" s="1" t="s">
         <v>228</v>
       </c>
@@ -4237,18 +4234,18 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>12277000</v>
+        <v>12373000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>11918000</v>
+        <v>11822000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>359000</v>
+        <v>551000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>
@@ -4285,23 +4282,17 @@
     <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f>B218+B222-C222</f>
-        <v>589000</v>
-      </c>
-      <c r="B222" s="8">
-        <v>230000</v>
-      </c>
+        <v>551000</v>
+      </c>
+      <c r="B222" s="8"/>
       <c r="C222" s="8"/>
-      <c r="D222" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>227</v>
-      </c>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
     </row>
     <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f>A222+B223-C223</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4311,7 +4302,7 @@
     <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" ref="A224:A231" si="17">A223+B224-C224</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4321,7 +4312,7 @@
     <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4331,7 +4322,7 @@
     <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4341,7 +4332,7 @@
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4351,7 +4342,7 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4361,7 +4352,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4371,7 +4362,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4381,7 +4372,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4391,7 +4382,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4401,7 +4392,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4411,7 +4402,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4421,7 +4412,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4431,7 +4422,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4441,7 +4432,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4451,7 +4442,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4461,7 +4452,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4471,7 +4462,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4481,7 +4472,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4491,18 +4482,18 @@
     <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="9">
         <f>SUM(B222:B241)+B216</f>
-        <v>12507000</v>
+        <v>12373000</v>
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
-        <v>11918000</v>
+        <v>11822000</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="232">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -706,6 +706,15 @@
   </si>
   <si>
     <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>کوصشر گوشی عرشیا</t>
+  </si>
+  <si>
+    <t>شومول</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1284,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4282,27 +4291,37 @@
     <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f>B218+B222-C222</f>
-        <v>551000</v>
+        <v>201000</v>
       </c>
       <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="1"/>
-      <c r="E222" s="1"/>
+      <c r="C222" s="8">
+        <v>350000</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f>A222+B223-C223</f>
-        <v>551000</v>
-      </c>
-      <c r="B223" s="8"/>
+        <v>301000</v>
+      </c>
+      <c r="B223" s="8">
+        <v>100000</v>
+      </c>
       <c r="C223" s="8"/>
-      <c r="D223" s="1"/>
+      <c r="D223" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="E223" s="1"/>
     </row>
     <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" ref="A224:A231" si="17">A223+B224-C224</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4312,7 +4331,7 @@
     <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4322,7 +4341,7 @@
     <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4332,7 +4351,7 @@
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4342,7 +4361,7 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4352,7 +4371,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4362,7 +4381,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4372,7 +4391,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4382,7 +4401,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4392,7 +4411,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4402,7 +4421,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4412,7 +4431,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4422,7 +4441,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4432,7 +4451,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4442,7 +4461,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4452,7 +4471,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4462,7 +4481,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4472,7 +4491,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4482,18 +4501,18 @@
     <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="9">
         <f>SUM(B222:B241)+B216</f>
-        <v>12373000</v>
+        <v>12473000</v>
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
-        <v>11822000</v>
+        <v>12172000</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="233">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -715,6 +715,9 @@
   </si>
   <si>
     <t>شومول</t>
+  </si>
+  <si>
+    <t>1405/07/13</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1287,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4321,17 +4324,23 @@
     <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" ref="A224:A231" si="17">A223+B224-C224</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B224" s="8"/>
-      <c r="C224" s="8"/>
-      <c r="D224" s="1"/>
-      <c r="E224" s="1"/>
+      <c r="C224" s="8">
+        <v>400000</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4341,7 +4350,7 @@
     <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4351,7 +4360,7 @@
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4361,7 +4370,7 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4371,7 +4380,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4381,7 +4390,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4391,7 +4400,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4401,7 +4410,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4411,7 +4420,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4421,7 +4430,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4431,7 +4440,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4441,7 +4450,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4451,7 +4460,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4461,7 +4470,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4471,7 +4480,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4481,7 +4490,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4491,7 +4500,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4505,14 +4514,14 @@
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
-        <v>12172000</v>
+        <v>12572000</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="234">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -718,6 +718,9 @@
   </si>
   <si>
     <t>1405/07/13</t>
+  </si>
+  <si>
+    <t>1405/07/14</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1290,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,17 +4343,23 @@
     <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
-      </c>
-      <c r="B225" s="8"/>
+        <v>-59000</v>
+      </c>
+      <c r="B225" s="8">
+        <v>40000</v>
+      </c>
       <c r="C225" s="8"/>
-      <c r="D225" s="1"/>
-      <c r="E225" s="1"/>
+      <c r="D225" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4360,7 +4369,7 @@
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4370,7 +4379,7 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4380,7 +4389,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4390,7 +4399,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4400,7 +4409,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4410,7 +4419,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4420,7 +4429,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4430,7 +4439,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4440,7 +4449,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4450,7 +4459,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4460,7 +4469,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4470,7 +4479,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4480,7 +4489,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4490,7 +4499,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4500,7 +4509,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4510,7 +4519,7 @@
     <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="9">
         <f>SUM(B222:B241)+B216</f>
-        <v>12473000</v>
+        <v>12513000</v>
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
@@ -4521,7 +4530,7 @@
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="235">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -721,6 +721,9 @@
   </si>
   <si>
     <t>1405/07/14</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4359,17 +4362,23 @@
     <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
-      </c>
-      <c r="B226" s="8"/>
+        <v>-9000</v>
+      </c>
+      <c r="B226" s="8">
+        <v>50000</v>
+      </c>
       <c r="C226" s="8"/>
-      <c r="D226" s="1"/>
-      <c r="E226" s="1"/>
+      <c r="D226" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4379,7 +4388,7 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4389,7 +4398,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4399,7 +4408,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4409,7 +4418,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4419,7 +4428,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4429,7 +4438,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4439,7 +4448,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4449,7 +4458,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4459,7 +4468,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4469,7 +4478,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4479,7 +4488,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4489,7 +4498,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4499,7 +4508,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4509,7 +4518,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4519,7 +4528,7 @@
     <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="9">
         <f>SUM(B222:B241)+B216</f>
-        <v>12513000</v>
+        <v>12563000</v>
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
@@ -4530,7 +4539,7 @@
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="237">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -724,6 +724,12 @@
   </si>
   <si>
     <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/29</t>
+  </si>
+  <si>
+    <t>وجه دنگ ویلا</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1299,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4378,17 +4384,23 @@
     <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="17"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B227" s="8"/>
-      <c r="C227" s="8"/>
-      <c r="D227" s="1"/>
-      <c r="E227" s="1"/>
+      <c r="C227" s="8">
+        <v>540000</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4398,7 +4410,7 @@
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4408,7 +4420,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4418,7 +4430,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4428,7 +4440,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4438,7 +4450,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4448,7 +4460,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4458,7 +4470,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4468,7 +4480,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4478,7 +4490,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4488,7 +4500,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4498,7 +4510,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4508,7 +4520,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4518,7 +4530,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4532,14 +4544,14 @@
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
-        <v>12572000</v>
+        <v>13112000</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="239">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -730,6 +730,12 @@
   </si>
   <si>
     <t>وجه دنگ ویلا</t>
+  </si>
+  <si>
+    <t>1405/08/04</t>
+  </si>
+  <si>
+    <t>اسپرسو پاپ کرن</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1305,7 @@
       </c>
       <c r="H2" s="9">
         <f>B244</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4400,17 +4406,23 @@
     <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="17"/>
-        <v>-549000</v>
-      </c>
-      <c r="B228" s="8"/>
+        <v>-184000</v>
+      </c>
+      <c r="B228" s="8">
+        <v>365000</v>
+      </c>
       <c r="C228" s="8"/>
-      <c r="D228" s="1"/>
-      <c r="E228" s="1"/>
+      <c r="D228" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="17"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4420,7 +4432,7 @@
     <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="17"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4430,7 +4442,7 @@
     <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="17"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4440,7 +4452,7 @@
     <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <f>A231+B232-C232</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -4450,7 +4462,7 @@
     <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <f t="shared" ref="A233" si="18">A232+B233-C233</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -4460,7 +4472,7 @@
     <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <f>A233+B234-C234</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -4470,7 +4482,7 @@
     <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -4480,7 +4492,7 @@
     <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4490,7 +4502,7 @@
     <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4500,7 +4512,7 @@
     <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4510,7 +4522,7 @@
     <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4520,7 +4532,7 @@
     <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4530,7 +4542,7 @@
     <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="19"/>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4540,7 +4552,7 @@
     <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" s="9">
         <f>SUM(B222:B241)+B216</f>
-        <v>12563000</v>
+        <v>12928000</v>
       </c>
       <c r="C242" s="9">
         <f>SUM(C222:C241)+C216</f>
@@ -4551,7 +4563,7 @@
     <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B244" s="15">
         <f>A241</f>
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>184</v>
